--- a/pipeline/credit_rating/output/sniratings_xhtn_20261027.xlsx
+++ b/pipeline/credit_rating/output/sniratings_xhtn_20261027.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="R2" s="1" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="R3" s="1" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="R4" s="1" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="R5" s="1" t="n">
@@ -853,7 +853,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="R6" s="1" t="n">
@@ -925,7 +925,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="R7" s="1" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="R8" s="1" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="R9" s="1" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="R10" s="1" t="n">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="R11" s="1" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="R12" s="1" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:08</t>
+          <t>2026-10-27 02:39:56</t>
         </is>
       </c>
       <c r="R13" s="1" t="n">

--- a/pipeline/credit_rating/output/sniratings_xhtn_20261027.xlsx
+++ b/pipeline/credit_rating/output/sniratings_xhtn_20261027.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,38 +515,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27/06/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Công ty TNHH Mặt Trời Vũng Tàu</t>
+          <t>Công ty Cổ phần Chứng khoán KAFI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bất động sản</t>
+          <t>Chứng khoán</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Tổ chức tài chính</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lần đầu</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Công cụ nợ</t>
-        </is>
-      </c>
+          <t>Giám sát Xếp hạng</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -555,20 +551,16 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2026/06/29163503/SVT-Public-Scan-1.pdf</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://sniratings.com.vn/?rating=cong-ty-tnhh-mat-troi-vung-tau</t>
+          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-chung-khoan-kafi-3</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>5793</v>
+        <v>6169</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -577,22 +569,22 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:56</t>
+          <t>2026-10-27 09:18:29</t>
         </is>
       </c>
       <c r="R2" s="1" t="n">
-        <v>46200</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Bluemarq Group</t>
+          <t>Công ty TNHH Xây dựng Dân dụng Phú Quốc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -607,19 +599,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Công cụ nợ</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Giám sát Xếp hạng</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Tích cực</t>
+          <t>Ổn định</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -628,11 +624,11 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-bluemarq-group</t>
+          <t>https://sniratings.com.vn/?rating=cong-ty-tnhh-xay-dung-dan-dung-phu-quoc-4</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>5800</v>
+        <v>6168</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -641,27 +637,27 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:56</t>
+          <t>2026-10-27 09:18:29</t>
         </is>
       </c>
       <c r="R3" s="1" t="n">
-        <v>46183</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Công nghệ Tài chính Encapital</t>
+          <t>Công ty TNHH Xây dựng Dân dụng Phú Quốc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Công nghệ thông tin</t>
+          <t>Bất động sản</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -678,7 +674,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -692,11 +688,11 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-cong-nghe-tai-chinh-encapital-2</t>
+          <t>https://sniratings.com.vn/?rating=cong-ty-tnhh-xay-dung-dan-dung-phu-quoc-3</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>5798</v>
+        <v>6167</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -705,32 +701,32 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:56</t>
+          <t>2026-10-27 09:18:29</t>
         </is>
       </c>
       <c r="R4" s="1" t="n">
-        <v>46170</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán KAFI</t>
+          <t>Công ty TNHH Mặt Trời Vũng Tàu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chứng khoán</t>
+          <t>Bất động sản</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tổ chức tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -740,13 +736,13 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tổ chức phát hành</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -757,22 +753,18 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2026/04/28163747/KAFI-Public.pdf</t>
+          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2026/06/29163503/SVT-Public-Scan-1.pdf</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2026/04/28163739/KAFI-Rating-Report.pdf</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-chung-khoan-kafi</t>
+          <t>https://sniratings.com.vn/?rating=cong-ty-tnhh-mat-troi-vung-tau</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>5575</v>
+        <v>5793</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -781,22 +773,22 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:56</t>
+          <t>2026-10-27 09:18:29</t>
         </is>
       </c>
       <c r="R5" s="1" t="n">
-        <v>46136</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Công ty TNHH Xây dựng Dân dụng Phú Quốc</t>
+          <t>Công ty Cổ phần Bluemarq Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -811,40 +803,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lần đầu</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Công cụ nợ</t>
-        </is>
-      </c>
+          <t>Giám sát Xếp hạng</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Ổn định</t>
+          <t>Tích cực</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2026/03/26162151/PCC-Bond-Public.pdf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://sniratings.com.vn/?rating=cong-ty-tnhh-xay-dung-dan-dung-phu-quoc-2</t>
+          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-bluemarq-group</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>5456</v>
+        <v>5800</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -853,27 +837,27 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:56</t>
+          <t>2026-10-27 09:18:29</t>
         </is>
       </c>
       <c r="R6" s="1" t="n">
-        <v>46105</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Công ty TNHH Xây dựng Dân dụng Phú Quốc</t>
+          <t>Công ty Cổ phần Công nghệ Tài chính Encapital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bất động sản</t>
+          <t>Công nghệ thông tin</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -883,18 +867,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lần đầu</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tổ chức phát hành</t>
-        </is>
-      </c>
+          <t>Giám sát Xếp hạng</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BB+</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -903,20 +883,16 @@
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2026/03/26161837/PCC-Corporate-Public.pdf</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://sniratings.com.vn/?rating=cong-ty-tnhh-xay-dung-dan-dung-phu-quoc</t>
+          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-cong-nghe-tai-chinh-encapital-2</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>5454</v>
+        <v>5798</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -925,32 +901,32 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:56</t>
+          <t>2026-10-27 09:18:29</t>
         </is>
       </c>
       <c r="R7" s="1" t="n">
-        <v>46105</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Đất Xanh</t>
+          <t>Công ty Cổ phần Chứng khoán KAFI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bất động sản</t>
+          <t>Chứng khoán</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Tổ chức tài chính</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -966,33 +942,33 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tích cực</t>
+          <t>Ổn định</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2025/12/11142639/DXG-Public.pdf</t>
+          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2026/04/28163747/KAFI-Public.pdf</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2025/12/11091425/DXG-Rating-Report.pdf</t>
+          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2026/04/28163739/KAFI-Rating-Report.pdf</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-tap-doan-dat-xanh</t>
+          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-chung-khoan-kafi</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>5262</v>
+        <v>5575</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1001,44 +977,48 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:56</t>
+          <t>2026-10-27 09:18:29</t>
         </is>
       </c>
       <c r="R8" s="1" t="n">
-        <v>46001</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán DNSE</t>
+          <t>Công ty TNHH Xây dựng Dân dụng Phú Quốc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chứng khoán</t>
+          <t>Bất động sản</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tổ chức tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Giám sát Xếp hạng</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>Lần đầu</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Công cụ nợ</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1047,16 +1027,20 @@
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2026/03/26162151/PCC-Bond-Public.pdf</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-chung-khoan-dnse-2</t>
+          <t>https://sniratings.com.vn/?rating=cong-ty-tnhh-xay-dung-dan-dung-phu-quoc-2</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>5258</v>
+        <v>5456</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1065,27 +1049,27 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:56</t>
+          <t>2026-10-27 09:18:29</t>
         </is>
       </c>
       <c r="R9" s="1" t="n">
-        <v>46001</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Công nghệ Tài chính Encapital</t>
+          <t>Công ty TNHH Xây dựng Dân dụng Phú Quốc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Công nghệ thông tin</t>
+          <t>Bất động sản</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1106,7 +1090,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1117,18 +1101,18 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2025/12/01133207/CBTT_XHTN_SI-ENCAP.pdf</t>
+          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2026/03/26161837/PCC-Corporate-Public.pdf</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-cong-nghe-tai-chinh-encapital</t>
+          <t>https://sniratings.com.vn/?rating=cong-ty-tnhh-xay-dung-dan-dung-phu-quoc</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>5239</v>
+        <v>5454</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1137,62 +1121,74 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:56</t>
+          <t>2026-10-27 09:18:29</t>
         </is>
       </c>
       <c r="R10" s="1" t="n">
-        <v>45989</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ngân Hàng TMCP Phương Đông</t>
+          <t>Công ty Cổ phần Tập đoàn Đất Xanh</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ngân hàng</t>
+          <t>Bất động sản</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tổ chức tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Giám sát Xếp hạng</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>Lần đầu</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tổ chức phát hành</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Ổn định</t>
+          <t>Tích cực</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2025/12/11142639/DXG-Public.pdf</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2025/12/11091425/DXG-Rating-Report.pdf</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://sniratings.com.vn/?rating=ngan-hang-tmcp-phuong-dong</t>
+          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-tap-doan-dat-xanh</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4941</v>
+        <v>5262</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1201,17 +1197,17 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:56</t>
+          <t>2026-10-27 09:18:29</t>
         </is>
       </c>
       <c r="R11" s="1" t="n">
-        <v>45910</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1231,14 +1227,10 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lần đầu</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tổ chức phát hành</t>
-        </is>
-      </c>
+          <t>Giám sát Xếp hạng</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
@@ -1251,20 +1243,16 @@
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2025/06/10143529/DNSE-Credit-Report-Summary.pdf</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-chung-khoan-dnse</t>
+          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-chung-khoan-dnse-2</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4708</v>
+        <v>5258</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1273,32 +1261,32 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:56</t>
+          <t>2026-10-27 09:18:29</t>
         </is>
       </c>
       <c r="R12" s="1" t="n">
-        <v>45818</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/03/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ngân Hàng TMCP Phương Đông</t>
+          <t>Công ty Cổ phần Công nghệ Tài chính Encapital</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ngân hàng</t>
+          <t>Công nghệ thông tin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tổ chức tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1314,7 +1302,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1325,30 +1313,238 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2025/03/10163537/OCB-Credit-Report-Summary.pdf</t>
+          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2025/12/01133207/CBTT_XHTN_SI-ENCAP.pdf</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
+          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-cong-nghe-tai-chinh-encapital</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>5239</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>S&amp;I Ratings</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:18:29</t>
+        </is>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>45989</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ngân Hàng TMCP Phương Đông</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ngân hàng</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tổ chức tài chính</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Giám sát Xếp hạng</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>https://sniratings.com.vn/?rating=ngan-hang-tmcp-phuong-dong</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>4941</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>S&amp;I Ratings</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:18:29</t>
+        </is>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>45910</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Công ty Cổ phần Chứng khoán DNSE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chứng khoán</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Tổ chức tài chính</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Lần đầu</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tổ chức phát hành</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2025/06/10143529/DNSE-Credit-Report-Summary.pdf</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>https://sniratings.com.vn/?rating=cong-ty-co-phan-chung-khoan-dnse</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>4708</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>S&amp;I Ratings</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:18:29</t>
+        </is>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>45818</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>10/03/2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ngân Hàng TMCP Phương Đông</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ngân hàng</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tổ chức tài chính</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Lần đầu</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tổ chức phát hành</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://sni-rating.s3.ap-southeast-1.amazonaws.com/wp-content/uploads/2025/03/10163537/OCB-Credit-Report-Summary.pdf</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>https://sniratings.com.vn/?rating=ngan-hang-tmcp-an-binh</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="O16" t="n">
         <v>591</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>S&amp;I Ratings</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2026-10-27 02:39:56</t>
-        </is>
-      </c>
-      <c r="R13" s="1" t="n">
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:18:29</t>
+        </is>
+      </c>
+      <c r="R16" s="1" t="n">
         <v>45726</v>
       </c>
     </row>

--- a/pipeline/credit_rating/output/sniratings_xhtn_20261027.xlsx
+++ b/pipeline/credit_rating/output/sniratings_xhtn_20261027.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R2" s="1" t="n">
@@ -637,7 +637,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R3" s="1" t="n">
@@ -701,7 +701,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R4" s="1" t="n">
@@ -773,7 +773,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R5" s="1" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R6" s="1" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R7" s="1" t="n">
@@ -977,7 +977,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R8" s="1" t="n">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R9" s="1" t="n">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R10" s="1" t="n">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R11" s="1" t="n">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R12" s="1" t="n">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R13" s="1" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R14" s="1" t="n">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R15" s="1" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:29</t>
+          <t>2026-10-27 14:51:10</t>
         </is>
       </c>
       <c r="R16" s="1" t="n">
